--- a/data/Telangana/Warangal (Urban)/Warangal (Urban)_Schools.xlsx
+++ b/data/Telangana/Warangal (Urban)/Warangal (Urban)_Schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,50 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>Contact School</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>St. Peters Central Public School</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>spcpswgl@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Old Bus Depot Road, Opp: Jerusalem Church, Hanamkonda</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0870-2579118</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Skill Stork International School</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>info@skillstork.org</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SVS Campus, Bheemaram, Hanamkonda, Warangal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8008880011</t>
         </is>
       </c>
     </row>
